--- a/data/HR_Dataset_Dirty.xlsx
+++ b/data/HR_Dataset_Dirty.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\Ellicium\DW assignment - Loparex\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E78F04C-9D63-4D64-A743-90337BE4E33C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="58">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -22,89 +28,179 @@
     <t>Name</t>
   </si>
   <si>
+    <t>Department</t>
+  </si>
+  <si>
     <t>Gender</t>
   </si>
   <si>
-    <t>Department</t>
+    <t>DateOfJoining</t>
   </si>
   <si>
     <t>ManagerID</t>
   </si>
   <si>
-    <t>DateOfJoining</t>
+    <t>Salary</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>Salary</t>
-  </si>
-  <si>
-    <t>Alice</t>
-  </si>
-  <si>
-    <t>bob</t>
-  </si>
-  <si>
-    <t>CHARLIE</t>
-  </si>
-  <si>
-    <t>Dana</t>
+    <t>Employee 1001</t>
+  </si>
+  <si>
+    <t>Employee 1002</t>
+  </si>
+  <si>
+    <t>Employee 1003</t>
+  </si>
+  <si>
+    <t>Employee 1004</t>
+  </si>
+  <si>
+    <t>Employee 1005</t>
+  </si>
+  <si>
+    <t>Employee 1006</t>
+  </si>
+  <si>
+    <t>Employee 1007</t>
+  </si>
+  <si>
+    <t>Employee 1008</t>
+  </si>
+  <si>
+    <t>Employee 1009</t>
+  </si>
+  <si>
+    <t>Employee 1010</t>
+  </si>
+  <si>
+    <t>Employee 1011</t>
+  </si>
+  <si>
+    <t>Employee 1012</t>
+  </si>
+  <si>
+    <t>Employee 1013</t>
+  </si>
+  <si>
+    <t>Employee 1014</t>
+  </si>
+  <si>
+    <t>Employee 1015</t>
+  </si>
+  <si>
+    <t>Employee 1016</t>
+  </si>
+  <si>
+    <t>Employee 1017</t>
+  </si>
+  <si>
+    <t>Employee 1018</t>
+  </si>
+  <si>
+    <t>Employee 1019</t>
+  </si>
+  <si>
+    <t>Employee 1020</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>It</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>F</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>f</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>hr</t>
-  </si>
-  <si>
-    <t>Human Resources</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Hr</t>
-  </si>
-  <si>
-    <t>2020-01-15</t>
-  </si>
-  <si>
-    <t>15/02/2020</t>
-  </si>
-  <si>
-    <t>2020.03.20</t>
-  </si>
-  <si>
-    <t>2020-04-25</t>
+    <t>2018-10-09</t>
+  </si>
+  <si>
+    <t>2017-03-06</t>
+  </si>
+  <si>
+    <t>2022-03-02</t>
+  </si>
+  <si>
+    <t>2016-01-03</t>
+  </si>
+  <si>
+    <t>15-01-2018</t>
+  </si>
+  <si>
+    <t>2022-02-09</t>
+  </si>
+  <si>
+    <t>2019-01-10</t>
+  </si>
+  <si>
+    <t>2016-02-16</t>
+  </si>
+  <si>
+    <t>2016-04-19</t>
+  </si>
+  <si>
+    <t>2017-09-05</t>
+  </si>
+  <si>
+    <t>2015-09-02</t>
+  </si>
+  <si>
+    <t>2019-11-13</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2020-05-12</t>
+  </si>
+  <si>
+    <t>2015-06-24</t>
+  </si>
+  <si>
+    <t>2017-04-15</t>
+  </si>
+  <si>
+    <t>2019-08-13</t>
+  </si>
+  <si>
+    <t>2017-08-13</t>
+  </si>
+  <si>
+    <t>2016-10-11</t>
+  </si>
+  <si>
+    <t>2017-02-20</t>
+  </si>
+  <si>
+    <t>Resigned</t>
   </si>
   <si>
     <t>Active</t>
-  </si>
-  <si>
-    <t>Resigned</t>
-  </si>
-  <si>
-    <t>active</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,13 +263,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -211,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -245,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -279,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -454,11 +560,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,131 +600,547 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2">
-        <v>1001</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>34</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2">
+        <v>2003</v>
+      </c>
+      <c r="G2">
+        <v>94088</v>
+      </c>
+      <c r="H2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>102</v>
+        <v>1002</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3">
+        <v>2003</v>
+      </c>
+      <c r="G3">
+        <v>91466</v>
+      </c>
+      <c r="H3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>103</v>
+        <v>1003</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
       <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4">
-        <v>1002</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H4">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4">
+        <v>2002</v>
+      </c>
+      <c r="G4">
+        <v>52179</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>104</v>
+        <v>1004</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5">
+        <v>2003</v>
+      </c>
+      <c r="G5">
+        <v>-10000</v>
+      </c>
+      <c r="H5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>1005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>2002</v>
+      </c>
+      <c r="G6">
+        <v>115497</v>
+      </c>
+      <c r="H6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>1006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7">
+        <v>2002</v>
+      </c>
+      <c r="G7">
+        <v>84898</v>
+      </c>
+      <c r="H7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>1007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8">
+        <v>2001</v>
+      </c>
+      <c r="G8">
+        <v>84167</v>
+      </c>
+      <c r="H8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>1008</v>
+      </c>
+      <c r="B9" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9">
+        <v>2001</v>
+      </c>
+      <c r="G9">
+        <v>94102</v>
+      </c>
+      <c r="H9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>1009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10">
+        <v>2003</v>
+      </c>
+      <c r="G10">
+        <v>107686</v>
+      </c>
+      <c r="H10" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11">
+        <v>2003</v>
+      </c>
+      <c r="G11">
+        <v>78999</v>
+      </c>
+      <c r="H11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>1011</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12">
+        <v>2002</v>
+      </c>
+      <c r="G12">
+        <v>54557</v>
+      </c>
+      <c r="H12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>1012</v>
+      </c>
+      <c r="B13" t="s">
         <v>19</v>
       </c>
-      <c r="E5">
-        <v>1003</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13">
+        <v>2001</v>
+      </c>
+      <c r="G13">
+        <v>72619</v>
+      </c>
+      <c r="H13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>1013</v>
+      </c>
+      <c r="B14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14">
+        <v>2002</v>
+      </c>
+      <c r="G14">
+        <v>80337</v>
+      </c>
+      <c r="H14" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>1014</v>
+      </c>
+      <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>2002</v>
+      </c>
+      <c r="G15">
+        <v>105771</v>
+      </c>
+      <c r="H15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>1015</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16">
+        <v>2001</v>
+      </c>
+      <c r="G16">
+        <v>87041</v>
+      </c>
+      <c r="H16" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>1016</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17">
+        <v>2001</v>
+      </c>
+      <c r="G17">
+        <v>99524</v>
+      </c>
+      <c r="H17" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>1017</v>
+      </c>
+      <c r="B18" t="s">
         <v>24</v>
       </c>
-      <c r="G5" t="s">
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18">
+        <v>2002</v>
+      </c>
+      <c r="G18">
+        <v>117150</v>
+      </c>
+      <c r="H18" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>1018</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19">
+        <v>2003</v>
+      </c>
+      <c r="G19">
+        <v>103744</v>
+      </c>
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>1019</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20">
+        <v>2003</v>
+      </c>
+      <c r="G20">
+        <v>108972</v>
+      </c>
+      <c r="H20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>1020</v>
+      </c>
+      <c r="B21" t="s">
         <v>27</v>
       </c>
-      <c r="H5">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6">
-        <v>101</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21">
+        <v>2002</v>
+      </c>
+      <c r="G21">
+        <v>102227</v>
+      </c>
+      <c r="H21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>1001</v>
+      </c>
+      <c r="B22" t="s">
         <v>8</v>
       </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>1001</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6">
-        <v>60000</v>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22">
+        <v>2003</v>
+      </c>
+      <c r="G22">
+        <v>94088</v>
+      </c>
+      <c r="H22" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
